--- a/data/trans_orig/IP19C04-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19C04-Edad-trans_orig.xlsx
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>709</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>6752</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>10190</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78231</t>
+          <t>77583</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83615</t>
+          <t>83626</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72889</t>
+          <t>72884</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154130</t>
+          <t>154563</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>161965</t>
+          <t>161901</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9135</t>
+          <t>9122</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15948</t>
+          <t>15589</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9394</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21566</t>
+          <t>21629</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90058</t>
+          <t>90071</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97288</t>
+          <t>97314</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89771</t>
+          <t>90130</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>100148</t>
+          <t>99917</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>183346</t>
+          <t>183283</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>195518</t>
+          <t>195617</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8574</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20349</t>
+          <t>20090</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>7914</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18507</t>
+          <t>18498</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19097</t>
+          <t>19533</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35072</t>
+          <t>34104</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143148</t>
+          <t>143407</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>154923</t>
+          <t>154794</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>155194</t>
+          <t>155203</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>165739</t>
+          <t>165787</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>302125</t>
+          <t>303093</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>318100</t>
+          <t>317664</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14119</t>
+          <t>13855</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28552</t>
+          <t>28870</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19093</t>
+          <t>18465</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35073</t>
+          <t>34049</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36529</t>
+          <t>35600</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58819</t>
+          <t>56580</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>322378</t>
+          <t>322060</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>336811</t>
+          <t>337075</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>326658</t>
+          <t>327682</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>342638</t>
+          <t>343266</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>653842</t>
+          <t>656081</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>676132</t>
+          <t>677061</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12403</t>
+          <t>12049</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2407</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10197</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19251</t>
+          <t>19281</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65285</t>
+          <t>65639</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74562</t>
+          <t>74440</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81867</t>
+          <t>81516</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89657</t>
+          <t>89730</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>150500</t>
+          <t>150470</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>163170</t>
+          <t>162446</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>3553</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11994</t>
+          <t>11535</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11916</t>
+          <t>12760</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>8836</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21116</t>
+          <t>20733</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113092</t>
+          <t>113551</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>121668</t>
+          <t>121533</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>120170</t>
+          <t>119326</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128515</t>
+          <t>128573</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>236056</t>
+          <t>236439</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>248325</t>
+          <t>248336</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13753</t>
+          <t>14138</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,47 +3724,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>8478</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4317</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14603</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>6,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>3,06%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8478</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4638</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>13975</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11353</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24732</t>
+          <t>24423</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>134167</t>
+          <t>133782</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143398</t>
+          <t>143149</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,49 +3837,49 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>96,77%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>132705</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>126580</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>136866</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>94,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>89,66%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>96,94%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>132705</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>127208</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>136545</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>90,1%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>96,71%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>395</t>
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>264371</t>
+          <t>264680</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>277750</t>
+          <t>277712</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31414</t>
+          <t>31640</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15142</t>
+          <t>14294</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29179</t>
+          <t>29573</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33459</t>
+          <t>33571</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55034</t>
+          <t>54266</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>322577</t>
+          <t>322351</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>338130</t>
+          <t>338332</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>336823</t>
+          <t>336429</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>350860</t>
+          <t>351708</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>664959</t>
+          <t>665727</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>686534</t>
+          <t>686422</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7092</t>
+          <t>7471</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>745</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7772</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11235</t>
+          <t>11104</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61551</t>
+          <t>61172</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67981</t>
+          <t>67573</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74357</t>
+          <t>74454</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81375</t>
+          <t>81384</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>139537</t>
+          <t>139668</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>148197</t>
+          <t>147922</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>9169</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21560</t>
+          <t>21063</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13848</t>
+          <t>13380</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15420</t>
+          <t>15359</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30955</t>
+          <t>30381</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>127357</t>
+          <t>127854</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>139787</t>
+          <t>139748</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>135493</t>
+          <t>135961</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145176</t>
+          <t>145188</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>267303</t>
+          <t>267877</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>282838</t>
+          <t>282899</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10537</t>
+          <t>10654</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139517</t>
+          <t>138870</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>144487</t>
+          <t>144474</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>128291</t>
+          <t>128238</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134560</t>
+          <t>134520</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>270459</t>
+          <t>270342</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>278295</t>
+          <t>278345</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13070</t>
+          <t>13357</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26731</t>
+          <t>27656</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9018</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21743</t>
+          <t>21615</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>25839</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44038</t>
+          <t>43764</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>336470</t>
+          <t>335545</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>350131</t>
+          <t>349844</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>346901</t>
+          <t>347029</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>359626</t>
+          <t>359390</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>687807</t>
+          <t>688081</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>706474</t>
+          <t>706006</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3508</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>7888</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>7563</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12385</t>
+          <t>11950</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58358</t>
+          <t>58308</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64372</t>
+          <t>64537</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>69081</t>
+          <t>69568</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76510</t>
+          <t>76466</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>130942</t>
+          <t>131377</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>140081</t>
+          <t>139865</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14369</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2549</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11297</t>
+          <t>11351</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9218</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21842</t>
+          <t>21800</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107534</t>
+          <t>107489</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>117107</t>
+          <t>117241</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153491</t>
+          <t>153437</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162239</t>
+          <t>162347</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264849</t>
+          <t>264891</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>277473</t>
+          <t>277607</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12757</t>
+          <t>13041</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12233</t>
+          <t>12408</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21163</t>
+          <t>20094</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>184980</t>
+          <t>184696</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>195429</t>
+          <t>195670</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>224975</t>
+          <t>224800</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>234329</t>
+          <t>234238</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>413782</t>
+          <t>414851</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>428810</t>
+          <t>427853</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11319</t>
+          <t>12298</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>27037</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9892</t>
+          <t>9669</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23604</t>
+          <t>23862</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25192</t>
+          <t>24239</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45601</t>
+          <t>45443</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>364133</t>
+          <t>364596</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>380314</t>
+          <t>379335</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>460840</t>
+          <t>460582</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>474552</t>
+          <t>474775</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>830475</t>
+          <t>830633</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>850884</t>
+          <t>851837</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C04-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19C04-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,47 +836,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3906</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3454</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1356</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7736</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,62%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2273</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>709</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6752</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6388</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,7%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,01%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3454</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1359</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7534</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10190</t>
+          <t>10260</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>76964</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>72682</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>79062</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>82062</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>77583</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>83626</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>77947</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>83980</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,3%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,99%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>76964</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>72884</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>79059</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,71%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154563</t>
+          <t>154493</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>161901</t>
+          <t>161979</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9932</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5627</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15769</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,39%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4559</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1879</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9122</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1971</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9078</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,6%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,2%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9932</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5802</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>15589</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,39%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9870</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21629</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>95787</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>89950</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>100092</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,61%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>85,08%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,68%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>94634</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>90071</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>97314</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>90115</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>97222</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,4%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,8%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>95787</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>90130</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>99917</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,61%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>183283</t>
+          <t>182494</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>195617</t>
+          <t>195042</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12234</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7385</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18350</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>13688</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8703</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>20090</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8377</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>19982</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,37%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,29%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12234</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7914</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>18498</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19533</t>
+          <t>19155</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34104</t>
+          <t>34311</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>161467</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>155351</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>166316</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,96%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,75%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>149809</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>143407</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>154794</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>143515</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>155120</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>91,63%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,71%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,68%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>161467</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>155203</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>165787</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>92,96%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>303093</t>
+          <t>302886</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>317664</t>
+          <t>318042</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25619</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18948</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>34357</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,08%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>20519</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13855</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>14407</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>28733</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,85%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>25619</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>18465</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>34049</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35600</t>
+          <t>36483</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56580</t>
+          <t>57423</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>336112</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>327374</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>342783</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,92%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,5%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,76%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>492</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>330411</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>322060</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>337075</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>322197</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>336523</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,15%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,77%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,05%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>336112</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>327682</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>343266</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>92,92%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>656081</t>
+          <t>655238</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>677061</t>
+          <t>676178</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2783,47 +2783,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3298</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5320</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10378</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>6807</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3248</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12049</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3485</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12526</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>8,76%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15,51%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5320</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2334</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>10548</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>7224</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19281</t>
+          <t>18695</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>86744</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>81686</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>89992</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,22%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>70881</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>65639</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>74440</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>65162</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>74203</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>91,24%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>84,49%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,82%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>86744</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>81516</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>89730</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,22%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>150470</t>
+          <t>151056</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>162446</t>
+          <t>162527</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>77688</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>77688</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>77688</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3361,102 +3361,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>7181</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3516</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12696</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,61%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>6808</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3553</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11535</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3377</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11356</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,44%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,22%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7181</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3513</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12760</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>9,08%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>13989</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>8651</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>20535</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>5,44%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>9,66%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>13989</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>8836</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>20733</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>5,44%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -3469,107 +3469,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>124905</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>119390</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>128570</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,56%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,39%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,34%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>118278</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>113551</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>121533</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>113730</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>121709</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,56%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,78%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>124905</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>119326</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>128573</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>90,92%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>97,3%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>243183</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>236637</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>248521</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>94,56%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>90,34%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>97,34%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>243183</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>236439</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>248336</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>94,56%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>125086</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>125086</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>125086</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8478</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4636</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14117</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>8605</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4771</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14138</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4922</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14437</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,82%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,56%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8478</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4317</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>14603</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,0%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24423</t>
+          <t>24336</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>132705</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>127066</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>136547</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>139315</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>133782</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>143149</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>133483</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>142998</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,18%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90,44%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,77%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>132705</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>126580</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>136866</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,0%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>264680</t>
+          <t>264767</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>277712</t>
+          <t>277510</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>141183</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>141183</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>141183</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>141183</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>141183</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>141183</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20978</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14563</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>28916</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5,73%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,9%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>22220</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>15659</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>31640</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>15946</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>31191</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>6,28%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,94%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>20978</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>14294</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>29573</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33571</t>
+          <t>33116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54266</t>
+          <t>55403</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>345024</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>337086</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>351439</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>94,27%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>92,1%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,02%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>472</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>331771</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>322351</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>338332</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>322800</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>338045</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>93,72%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,06%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,58%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>345024</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>336429</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>351708</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>94,27%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>665727</t>
+          <t>664590</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>686422</t>
+          <t>686877</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>504</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4730,47 +4730,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>536</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>536</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4965,67 +4965,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>3196</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7699</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,37%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>2839</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7471</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6437</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,14%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,88%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3196</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>745</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7675</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11104</t>
+          <t>11751</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>78933</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>74430</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>81278</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,63%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>65804</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>61172</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>67573</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>62206</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>68008</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,86%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,44%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>78933</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>74454</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>81384</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,11%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>139668</t>
+          <t>139021</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>147922</t>
+          <t>148039</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>68643</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>68643</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>68643</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7796</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4041</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13417</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,22%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,98%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>13887</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9169</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>21063</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8487</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>20789</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>9,33%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,14%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7796</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4153</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13380</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15359</t>
+          <t>15011</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30381</t>
+          <t>29803</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>141545</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>135924</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>145300</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,78%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,02%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,29%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>135030</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>127854</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>139748</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>128128</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>140430</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>90,67%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>85,86%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,84%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>141545</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>135961</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>145188</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,78%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>267877</t>
+          <t>268455</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>282899</t>
+          <t>283247</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>148917</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>148917</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>148917</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3453</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1348</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7005</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2454</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6235</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6020</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,69%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3453</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1371</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7653</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10654</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -5759,74 +5759,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>132438</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>128886</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>134543</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,46%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,84%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,01%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>142651</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>138870</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>144474</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>139085</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>144478</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,31%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,7%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,85%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,57%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>132438</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>128238</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>134520</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,46%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>94,37%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,99%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>383</t>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>270342</t>
+          <t>270595</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>278345</t>
+          <t>278324</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>135891</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>135891</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>135891</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>145105</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>145105</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>145105</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>135891</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>135891</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>135891</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14445</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8866</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>22080</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,99%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>19181</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13357</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>27656</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>13055</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>27246</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,28%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>14445</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>9254</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>21615</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25839</t>
+          <t>24962</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43764</t>
+          <t>44272</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>354199</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>346564</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>359778</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>94,01%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,6%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>500</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>344020</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>335545</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>349844</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>335955</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>350146</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,72%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,39%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>354199</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>347029</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>359390</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>688081</t>
+          <t>687573</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>706006</t>
+          <t>706883</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>368644</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>368644</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>368644</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>528</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>363201</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>363201</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>363201</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>368644</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>368644</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>368644</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,107 +6564,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12,08%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>51,33%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3156</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>13,3%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2941</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>59,37%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3340</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4111</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2275</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>87,92%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>48,65%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>6072</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>4609</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2210</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5316</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>86,7%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>41,57%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>18</t>
@@ -6752,27 +6752,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>10406</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2418</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7031</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,41%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4022</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1659</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7888</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,92%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7563</t>
+          <t>7874</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6773</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11950</t>
+          <t>11616</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>65152</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>60539</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>67046</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,42%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,59%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>62174</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>58308</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>64537</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>93,92%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,49%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>74380</t>
+          <t>59581</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>69568</t>
+          <t>55575</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76466</t>
+          <t>61653</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>136554</t>
+          <t>124734</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>131377</t>
+          <t>119404</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>139865</t>
+          <t>127999</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>67570</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>67570</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>67570</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>143327</t>
+          <t>131020</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>143327</t>
+          <t>131020</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>143327</t>
+          <t>131020</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5393</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2275</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10616</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,84%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8671</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4662</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14414</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,11%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11351</t>
+          <t>14684</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14398</t>
+          <t>14239</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>8415</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21800</t>
+          <t>21497</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>149905</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>144682</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>153023</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,16%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,54%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>113232</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>107489</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>117241</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>92,89%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,18%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>159061</t>
+          <t>112994</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153437</t>
+          <t>107156</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162347</t>
+          <t>117449</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>272293</t>
+          <t>262899</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264891</t>
+          <t>255641</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>277607</t>
+          <t>268723</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>155298</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>155298</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>155298</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>121903</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>121903</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>121903</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>277138</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>277138</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>277138</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6057</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2866</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12582</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5686</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2067</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13041</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12408</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>12109</t>
+          <t>10567</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7092</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20094</t>
+          <t>17652</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>227493</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>220968</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>230684</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,41%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,61%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>192051</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>184696</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>195670</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>97,12%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,4%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>230784</t>
+          <t>200406</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>224800</t>
+          <t>195803</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>234238</t>
+          <t>202876</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>422836</t>
+          <t>427899</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>414851</t>
+          <t>420814</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>427853</t>
+          <t>432387</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>233550</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>233550</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>233550</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>197737</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>197737</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>197737</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>204916</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>204916</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>204916</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14433</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8914</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>22960</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>18379</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12298</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>27037</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15609</t>
+          <t>17224</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23862</t>
+          <t>25018</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>33988</t>
+          <t>31657</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24239</t>
+          <t>22739</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45443</t>
+          <t>42952</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>446662</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>438135</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>452181</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,87%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,02%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>528</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>373254</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>364596</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>379335</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>95,31%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>93,1%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,86%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>468835</t>
+          <t>379054</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>460582</t>
+          <t>371260</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>474775</t>
+          <t>384751</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>842088</t>
+          <t>825715</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>830633</t>
+          <t>814420</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>851837</t>
+          <t>834633</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
